--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1156"/>
+  <dimension ref="A1:F1157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23535,16 +23535,36 @@
         <v>12.25</v>
       </c>
       <c r="C1156" t="n">
-        <v>12.46</v>
+        <v>12.46000003814697</v>
       </c>
       <c r="D1156" t="n">
-        <v>11.97</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="E1156" t="n">
-        <v>11.97</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="F1156" t="n">
         <v>9880608</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B1157" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="C1157" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>656858</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -23552,10 +23552,10 @@
         <v>46231</v>
       </c>
       <c r="B1157" t="n">
-        <v>12.34</v>
+        <v>12.47</v>
       </c>
       <c r="C1157" t="n">
-        <v>12.52</v>
+        <v>12.61</v>
       </c>
       <c r="D1157" t="n">
         <v>12.29</v>
@@ -23564,7 +23564,7 @@
         <v>12.37</v>
       </c>
       <c r="F1157" t="n">
-        <v>656858</v>
+        <v>3812606</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -23564,7 +23564,7 @@
         <v>12.37</v>
       </c>
       <c r="F1157" t="n">
-        <v>3812606</v>
+        <v>4920058</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -23552,16 +23552,16 @@
         <v>46231</v>
       </c>
       <c r="B1157" t="n">
-        <v>12.47</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="C1157" t="n">
-        <v>12.61</v>
+        <v>12.60999965667725</v>
       </c>
       <c r="D1157" t="n">
-        <v>12.29</v>
+        <v>12.28999996185303</v>
       </c>
       <c r="E1157" t="n">
-        <v>12.37</v>
+        <v>12.36999988555908</v>
       </c>
       <c r="F1157" t="n">
         <v>4920058</v>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1157"/>
+  <dimension ref="A1:F1158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23567,6 +23567,26 @@
         <v>4920058</v>
       </c>
     </row>
+    <row r="1158">
+      <c r="A1158" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B1158" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="C1158" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>3340799</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -23572,19 +23572,19 @@
         <v>46232</v>
       </c>
       <c r="B1158" t="n">
-        <v>12.08</v>
+        <v>11.98</v>
       </c>
       <c r="C1158" t="n">
         <v>12.47</v>
       </c>
       <c r="D1158" t="n">
-        <v>12.03</v>
+        <v>11.94</v>
       </c>
       <c r="E1158" t="n">
         <v>12.47</v>
       </c>
       <c r="F1158" t="n">
-        <v>3340799</v>
+        <v>5014997</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1158"/>
+  <dimension ref="A1:F1159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23572,19 +23572,39 @@
         <v>46232</v>
       </c>
       <c r="B1158" t="n">
-        <v>11.98</v>
+        <v>11.97999954223633</v>
       </c>
       <c r="C1158" t="n">
-        <v>12.47</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="D1158" t="n">
-        <v>11.94</v>
+        <v>11.9399995803833</v>
       </c>
       <c r="E1158" t="n">
-        <v>12.47</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="F1158" t="n">
         <v>5014997</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B1159" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="C1159" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>3580487</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1159"/>
+  <dimension ref="A1:F1160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23592,19 +23592,39 @@
         <v>46233</v>
       </c>
       <c r="B1159" t="n">
-        <v>12.23</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="C1159" t="n">
-        <v>12.23</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="D1159" t="n">
-        <v>11.86</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="E1159" t="n">
-        <v>12.1</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="F1159" t="n">
         <v>3580487</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B1160" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="C1160" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>4594183</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1160"/>
+  <dimension ref="A1:F1161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23612,19 +23612,39 @@
         <v>46234</v>
       </c>
       <c r="B1160" t="n">
+        <v>12.05000019073486</v>
+      </c>
+      <c r="C1160" t="n">
+        <v>12.27999973297119</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>12.02000045776367</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>12.27999973297119</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>4594763</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B1161" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="C1161" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="D1161" t="n">
         <v>12.05</v>
       </c>
-      <c r="C1160" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="D1160" t="n">
-        <v>12.02</v>
-      </c>
-      <c r="E1160" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="F1160" t="n">
-        <v>4594183</v>
+      <c r="E1161" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>4549045</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -23609,42 +23609,42 @@
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1160" t="n">
+        <v>12.17000007629395</v>
+      </c>
+      <c r="C1160" t="n">
+        <v>12.27000045776367</v>
+      </c>
+      <c r="D1160" t="n">
         <v>12.05000019073486</v>
       </c>
-      <c r="C1160" t="n">
-        <v>12.27999973297119</v>
-      </c>
-      <c r="D1160" t="n">
-        <v>12.02000045776367</v>
-      </c>
       <c r="E1160" t="n">
-        <v>12.27999973297119</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="F1160" t="n">
-        <v>4594763</v>
+        <v>4549045</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1161" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="C1161" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="D1161" t="n">
         <v>12.17</v>
       </c>
-      <c r="C1161" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="D1161" t="n">
-        <v>12.05</v>
-      </c>
       <c r="E1161" t="n">
-        <v>12.06</v>
+        <v>12.24</v>
       </c>
       <c r="F1161" t="n">
-        <v>4549045</v>
+        <v>4709084</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1161"/>
+  <dimension ref="A1:F1163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23609,42 +23609,82 @@
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B1160" t="n">
-        <v>12.17000007629395</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="C1160" t="n">
-        <v>12.27000045776367</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="D1160" t="n">
-        <v>12.05000019073486</v>
+        <v>12.02000045776367</v>
       </c>
       <c r="E1160" t="n">
-        <v>12.0600004196167</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="F1160" t="n">
-        <v>4549045</v>
+        <v>4594763</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B1161" t="n">
+        <v>12.17000007629395</v>
+      </c>
+      <c r="C1161" t="n">
+        <v>12.27000045776367</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>12.05000019073486</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>12.0600004196167</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>4549045</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="B1161" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="C1161" t="n">
-        <v>12.47</v>
-      </c>
-      <c r="D1161" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="E1161" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="F1161" t="n">
+      <c r="B1162" t="n">
+        <v>12.18000030517578</v>
+      </c>
+      <c r="C1162" t="n">
+        <v>12.47000026702881</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>12.17000007629395</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>12.23999977111816</v>
+      </c>
+      <c r="F1162" t="n">
         <v>4709084</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B1163" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="C1163" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>3875531</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1163"/>
+  <dimension ref="A1:F1164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23672,19 +23672,39 @@
         <v>46239</v>
       </c>
       <c r="B1163" t="n">
-        <v>12.31</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="C1163" t="n">
-        <v>12.44</v>
+        <v>12.4399995803833</v>
       </c>
       <c r="D1163" t="n">
-        <v>12.2</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="E1163" t="n">
-        <v>12.3</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="F1163" t="n">
         <v>3875531</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1164" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="C1164" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>14181318</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -23609,102 +23609,102 @@
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1160" t="n">
+        <v>12.17000007629395</v>
+      </c>
+      <c r="C1160" t="n">
+        <v>12.27000045776367</v>
+      </c>
+      <c r="D1160" t="n">
         <v>12.05000019073486</v>
       </c>
-      <c r="C1160" t="n">
-        <v>12.27999973297119</v>
-      </c>
-      <c r="D1160" t="n">
-        <v>12.02000045776367</v>
-      </c>
       <c r="E1160" t="n">
-        <v>12.27999973297119</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="F1160" t="n">
-        <v>4594763</v>
+        <v>4549045</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1161" t="n">
+        <v>12.18000030517578</v>
+      </c>
+      <c r="C1161" t="n">
+        <v>12.47000026702881</v>
+      </c>
+      <c r="D1161" t="n">
         <v>12.17000007629395</v>
       </c>
-      <c r="C1161" t="n">
-        <v>12.27000045776367</v>
-      </c>
-      <c r="D1161" t="n">
-        <v>12.05000019073486</v>
-      </c>
       <c r="E1161" t="n">
-        <v>12.0600004196167</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="F1161" t="n">
-        <v>4549045</v>
+        <v>4709084</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1162" t="n">
-        <v>12.18000030517578</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="C1162" t="n">
-        <v>12.47000026702881</v>
+        <v>12.4399995803833</v>
       </c>
       <c r="D1162" t="n">
-        <v>12.17000007629395</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="E1162" t="n">
-        <v>12.23999977111816</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="F1162" t="n">
-        <v>4709084</v>
+        <v>3875531</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1163" t="n">
-        <v>12.3100004196167</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="C1163" t="n">
-        <v>12.4399995803833</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="D1163" t="n">
-        <v>12.19999980926514</v>
+        <v>11.88000011444092</v>
       </c>
       <c r="E1163" t="n">
-        <v>12.30000019073486</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="F1163" t="n">
-        <v>3875531</v>
+        <v>14181318</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1164" t="n">
-        <v>11.97</v>
+        <v>11.6</v>
       </c>
       <c r="C1164" t="n">
-        <v>12.3</v>
+        <v>12.13</v>
       </c>
       <c r="D1164" t="n">
-        <v>11.88</v>
+        <v>11.6</v>
       </c>
       <c r="E1164" t="n">
-        <v>12.27</v>
+        <v>12.03</v>
       </c>
       <c r="F1164" t="n">
-        <v>14181318</v>
+        <v>10094068</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1164"/>
+  <dimension ref="A1:F1166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23609,102 +23609,142 @@
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B1160" t="n">
-        <v>12.17000007629395</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="C1160" t="n">
-        <v>12.27000045776367</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="D1160" t="n">
-        <v>12.05000019073486</v>
+        <v>12.02000045776367</v>
       </c>
       <c r="E1160" t="n">
-        <v>12.0600004196167</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="F1160" t="n">
-        <v>4549045</v>
+        <v>4594763</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B1161" t="n">
-        <v>12.18000030517578</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="C1161" t="n">
-        <v>12.47000026702881</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="D1161" t="n">
-        <v>12.17000007629395</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="E1161" t="n">
-        <v>12.23999977111816</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="F1161" t="n">
-        <v>4709084</v>
+        <v>4549045</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B1162" t="n">
-        <v>12.3100004196167</v>
+        <v>12.18000030517578</v>
       </c>
       <c r="C1162" t="n">
-        <v>12.4399995803833</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="D1162" t="n">
-        <v>12.19999980926514</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="E1162" t="n">
-        <v>12.30000019073486</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="F1162" t="n">
-        <v>3875531</v>
+        <v>4709084</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B1163" t="n">
-        <v>11.97000026702881</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="C1163" t="n">
+        <v>12.4399995803833</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>12.19999980926514</v>
+      </c>
+      <c r="E1163" t="n">
         <v>12.30000019073486</v>
       </c>
-      <c r="D1163" t="n">
-        <v>11.88000011444092</v>
-      </c>
-      <c r="E1163" t="n">
-        <v>12.27000045776367</v>
-      </c>
       <c r="F1163" t="n">
-        <v>14181318</v>
+        <v>3875531</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1164" t="n">
+        <v>11.97000026702881</v>
+      </c>
+      <c r="C1164" t="n">
+        <v>12.30000019073486</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>11.88000011444092</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>12.27000045776367</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>14181318</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="1" t="n">
         <v>46241</v>
       </c>
-      <c r="B1164" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="C1164" t="n">
-        <v>12.13</v>
-      </c>
-      <c r="D1164" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="E1164" t="n">
-        <v>12.03</v>
-      </c>
-      <c r="F1164" t="n">
+      <c r="B1165" t="n">
+        <v>11.60000038146973</v>
+      </c>
+      <c r="C1165" t="n">
+        <v>12.13000011444092</v>
+      </c>
+      <c r="D1165" t="n">
+        <v>11.60000038146973</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>12.02999973297119</v>
+      </c>
+      <c r="F1165" t="n">
         <v>10094068</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B1166" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="C1166" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="D1166" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>3210994</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1166"/>
+  <dimension ref="A1:F1167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23732,19 +23732,39 @@
         <v>46244</v>
       </c>
       <c r="B1166" t="n">
-        <v>11.73</v>
+        <v>11.72999954223633</v>
       </c>
       <c r="C1166" t="n">
-        <v>11.86</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="D1166" t="n">
-        <v>11.59</v>
+        <v>11.59000015258789</v>
       </c>
       <c r="E1166" t="n">
-        <v>11.66</v>
+        <v>11.65999984741211</v>
       </c>
       <c r="F1166" t="n">
         <v>3210994</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B1167" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="C1167" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>9590947</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1167"/>
+  <dimension ref="A1:F1166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23609,162 +23609,142 @@
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1160" t="n">
+        <v>12.17000007629395</v>
+      </c>
+      <c r="C1160" t="n">
+        <v>12.27000045776367</v>
+      </c>
+      <c r="D1160" t="n">
         <v>12.05000019073486</v>
       </c>
-      <c r="C1160" t="n">
-        <v>12.27999973297119</v>
-      </c>
-      <c r="D1160" t="n">
-        <v>12.02000045776367</v>
-      </c>
       <c r="E1160" t="n">
-        <v>12.27999973297119</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="F1160" t="n">
-        <v>4594763</v>
+        <v>4549045</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1161" t="n">
+        <v>12.18000030517578</v>
+      </c>
+      <c r="C1161" t="n">
+        <v>12.47000026702881</v>
+      </c>
+      <c r="D1161" t="n">
         <v>12.17000007629395</v>
       </c>
-      <c r="C1161" t="n">
-        <v>12.27000045776367</v>
-      </c>
-      <c r="D1161" t="n">
-        <v>12.05000019073486</v>
-      </c>
       <c r="E1161" t="n">
-        <v>12.0600004196167</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="F1161" t="n">
-        <v>4549045</v>
+        <v>4709084</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1162" t="n">
-        <v>12.18000030517578</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="C1162" t="n">
-        <v>12.47000026702881</v>
+        <v>12.4399995803833</v>
       </c>
       <c r="D1162" t="n">
-        <v>12.17000007629395</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="E1162" t="n">
-        <v>12.23999977111816</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="F1162" t="n">
-        <v>4709084</v>
+        <v>3875531</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1163" t="n">
-        <v>12.3100004196167</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="C1163" t="n">
-        <v>12.4399995803833</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="D1163" t="n">
-        <v>12.19999980926514</v>
+        <v>11.88000011444092</v>
       </c>
       <c r="E1163" t="n">
-        <v>12.30000019073486</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="F1163" t="n">
-        <v>3875531</v>
+        <v>14181318</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1164" t="n">
-        <v>11.97000026702881</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="C1164" t="n">
-        <v>12.30000019073486</v>
+        <v>12.13000011444092</v>
       </c>
       <c r="D1164" t="n">
-        <v>11.88000011444092</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="E1164" t="n">
-        <v>12.27000045776367</v>
+        <v>12.02999973297119</v>
       </c>
       <c r="F1164" t="n">
-        <v>14181318</v>
+        <v>10094068</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B1165" t="n">
-        <v>11.60000038146973</v>
+        <v>11.63000011444092</v>
       </c>
       <c r="C1165" t="n">
-        <v>12.13000011444092</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="D1165" t="n">
-        <v>11.60000038146973</v>
+        <v>11.46000003814697</v>
       </c>
       <c r="E1165" t="n">
-        <v>12.02999973297119</v>
+        <v>11.78999996185303</v>
       </c>
       <c r="F1165" t="n">
-        <v>10094068</v>
+        <v>9590947</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B1166" t="n">
-        <v>11.72999954223633</v>
+        <v>11.61</v>
       </c>
       <c r="C1166" t="n">
-        <v>11.85999965667725</v>
+        <v>11.82</v>
       </c>
       <c r="D1166" t="n">
-        <v>11.59000015258789</v>
+        <v>11.46</v>
       </c>
       <c r="E1166" t="n">
-        <v>11.65999984741211</v>
+        <v>11.66</v>
       </c>
       <c r="F1166" t="n">
-        <v>3210994</v>
-      </c>
-    </row>
-    <row r="1167">
-      <c r="A1167" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B1167" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="C1167" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="D1167" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="E1167" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="F1167" t="n">
-        <v>9590947</v>
+        <v>13093870</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1166"/>
+  <dimension ref="A1:F1167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23732,19 +23732,39 @@
         <v>46246</v>
       </c>
       <c r="B1166" t="n">
-        <v>11.61</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="C1166" t="n">
-        <v>11.82</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="D1166" t="n">
-        <v>11.46</v>
+        <v>11.46000003814697</v>
       </c>
       <c r="E1166" t="n">
-        <v>11.66</v>
+        <v>11.65999984741211</v>
       </c>
       <c r="F1166" t="n">
         <v>13093870</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B1167" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="C1167" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>6381643</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1167"/>
+  <dimension ref="A1:F1168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23429,282 +23429,282 @@
     </row>
     <row r="1151">
       <c r="A1151" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B1151" t="n">
-        <v>11.81999969482422</v>
+        <v>12.07999992370605</v>
       </c>
       <c r="C1151" t="n">
-        <v>12.01000022888184</v>
+        <v>12.10999965667725</v>
       </c>
       <c r="D1151" t="n">
-        <v>11.5</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="E1151" t="n">
-        <v>11.5</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="F1151" t="n">
-        <v>6917063</v>
+        <v>6399437</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B1152" t="n">
-        <v>12.07999992370605</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="C1152" t="n">
-        <v>12.10999965667725</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="D1152" t="n">
-        <v>11.69999980926514</v>
+        <v>11.71000003814697</v>
       </c>
       <c r="E1152" t="n">
-        <v>11.85000038146973</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="F1152" t="n">
-        <v>6399437</v>
+        <v>5815264</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B1153" t="n">
-        <v>12.10000038146973</v>
+        <v>12.09000015258789</v>
       </c>
       <c r="C1153" t="n">
-        <v>12.23999977111816</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="D1153" t="n">
-        <v>11.71000003814697</v>
+        <v>11.9399995803833</v>
       </c>
       <c r="E1153" t="n">
-        <v>12.10000038146973</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="F1153" t="n">
-        <v>5815264</v>
+        <v>3000855</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B1154" t="n">
+        <v>11.81999969482422</v>
+      </c>
+      <c r="C1154" t="n">
         <v>12.09000015258789</v>
       </c>
-      <c r="C1154" t="n">
-        <v>12.27000045776367</v>
-      </c>
       <c r="D1154" t="n">
-        <v>11.9399995803833</v>
+        <v>11.81999969482422</v>
       </c>
       <c r="E1154" t="n">
-        <v>12.05000019073486</v>
+        <v>12.06999969482422</v>
       </c>
       <c r="F1154" t="n">
-        <v>3000855</v>
+        <v>3072424</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B1155" t="n">
-        <v>11.81999969482422</v>
+        <v>12.25</v>
       </c>
       <c r="C1155" t="n">
-        <v>12.09000015258789</v>
+        <v>12.46000003814697</v>
       </c>
       <c r="D1155" t="n">
-        <v>11.81999969482422</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="E1155" t="n">
-        <v>12.06999969482422</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="F1155" t="n">
-        <v>3072424</v>
+        <v>9880608</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B1156" t="n">
-        <v>12.25</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="C1156" t="n">
-        <v>12.46000003814697</v>
+        <v>12.60999965667725</v>
       </c>
       <c r="D1156" t="n">
-        <v>11.97000026702881</v>
+        <v>12.28999996185303</v>
       </c>
       <c r="E1156" t="n">
-        <v>11.97000026702881</v>
+        <v>12.36999988555908</v>
       </c>
       <c r="F1156" t="n">
-        <v>9880608</v>
+        <v>4920058</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B1157" t="n">
+        <v>11.97999954223633</v>
+      </c>
+      <c r="C1157" t="n">
         <v>12.47000026702881</v>
       </c>
-      <c r="C1157" t="n">
-        <v>12.60999965667725</v>
-      </c>
       <c r="D1157" t="n">
-        <v>12.28999996185303</v>
+        <v>11.9399995803833</v>
       </c>
       <c r="E1157" t="n">
-        <v>12.36999988555908</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="F1157" t="n">
-        <v>4920058</v>
+        <v>5014997</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B1158" t="n">
-        <v>11.97999954223633</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="C1158" t="n">
-        <v>12.47000026702881</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="D1158" t="n">
-        <v>11.9399995803833</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="E1158" t="n">
-        <v>12.47000026702881</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="F1158" t="n">
-        <v>5014997</v>
+        <v>3580487</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B1159" t="n">
-        <v>12.22999954223633</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="C1159" t="n">
-        <v>12.22999954223633</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="D1159" t="n">
-        <v>11.85999965667725</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="E1159" t="n">
-        <v>12.10000038146973</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="F1159" t="n">
-        <v>3580487</v>
+        <v>4549045</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1160" t="n">
+        <v>12.18000030517578</v>
+      </c>
+      <c r="C1160" t="n">
+        <v>12.47000026702881</v>
+      </c>
+      <c r="D1160" t="n">
         <v>12.17000007629395</v>
       </c>
-      <c r="C1160" t="n">
-        <v>12.27000045776367</v>
-      </c>
-      <c r="D1160" t="n">
-        <v>12.05000019073486</v>
-      </c>
       <c r="E1160" t="n">
-        <v>12.0600004196167</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="F1160" t="n">
-        <v>4549045</v>
+        <v>4709084</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1161" t="n">
-        <v>12.18000030517578</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="C1161" t="n">
-        <v>12.47000026702881</v>
+        <v>12.4399995803833</v>
       </c>
       <c r="D1161" t="n">
-        <v>12.17000007629395</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="E1161" t="n">
-        <v>12.23999977111816</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="F1161" t="n">
-        <v>4709084</v>
+        <v>3875531</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1162" t="n">
-        <v>12.3100004196167</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="C1162" t="n">
-        <v>12.4399995803833</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="D1162" t="n">
-        <v>12.19999980926514</v>
+        <v>11.88000011444092</v>
       </c>
       <c r="E1162" t="n">
-        <v>12.30000019073486</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="F1162" t="n">
-        <v>3875531</v>
+        <v>14181318</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1163" t="n">
-        <v>11.97000026702881</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="C1163" t="n">
-        <v>12.30000019073486</v>
+        <v>12.13000011444092</v>
       </c>
       <c r="D1163" t="n">
-        <v>11.88000011444092</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="E1163" t="n">
-        <v>12.27000045776367</v>
+        <v>12.02999973297119</v>
       </c>
       <c r="F1163" t="n">
-        <v>14181318</v>
+        <v>10094068</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B1164" t="n">
-        <v>11.60000038146973</v>
+        <v>11.72999954223633</v>
       </c>
       <c r="C1164" t="n">
-        <v>12.13000011444092</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="D1164" t="n">
-        <v>11.60000038146973</v>
+        <v>11.59000015258789</v>
       </c>
       <c r="E1164" t="n">
-        <v>12.02999973297119</v>
+        <v>11.65999984741211</v>
       </c>
       <c r="F1164" t="n">
-        <v>10094068</v>
+        <v>3210994</v>
       </c>
     </row>
     <row r="1165">
@@ -23752,19 +23752,39 @@
         <v>46247</v>
       </c>
       <c r="B1167" t="n">
-        <v>12.04</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="C1167" t="n">
-        <v>12.04</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="D1167" t="n">
-        <v>11.57</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="E1167" t="n">
-        <v>11.61</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="F1167" t="n">
         <v>6381643</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B1168" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="C1168" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="D1168" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>35211169</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1168"/>
+  <dimension ref="A1:F1169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23429,282 +23429,282 @@
     </row>
     <row r="1151">
       <c r="A1151" s="1" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B1151" t="n">
-        <v>12.07999992370605</v>
+        <v>11.81999969482422</v>
       </c>
       <c r="C1151" t="n">
-        <v>12.10999965667725</v>
+        <v>12.01000022888184</v>
       </c>
       <c r="D1151" t="n">
-        <v>11.69999980926514</v>
+        <v>11.5</v>
       </c>
       <c r="E1151" t="n">
-        <v>11.85000038146973</v>
+        <v>11.5</v>
       </c>
       <c r="F1151" t="n">
-        <v>6399437</v>
+        <v>6917063</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" s="1" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B1152" t="n">
-        <v>12.10000038146973</v>
+        <v>12.07999992370605</v>
       </c>
       <c r="C1152" t="n">
-        <v>12.23999977111816</v>
+        <v>12.10999965667725</v>
       </c>
       <c r="D1152" t="n">
-        <v>11.71000003814697</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="E1152" t="n">
-        <v>12.10000038146973</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="F1152" t="n">
-        <v>5815264</v>
+        <v>6399437</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" s="1" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B1153" t="n">
-        <v>12.09000015258789</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="C1153" t="n">
-        <v>12.27000045776367</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="D1153" t="n">
-        <v>11.9399995803833</v>
+        <v>11.71000003814697</v>
       </c>
       <c r="E1153" t="n">
-        <v>12.05000019073486</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="F1153" t="n">
-        <v>3000855</v>
+        <v>5815264</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" s="1" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B1154" t="n">
-        <v>11.81999969482422</v>
+        <v>12.09000015258789</v>
       </c>
       <c r="C1154" t="n">
-        <v>12.09000015258789</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="D1154" t="n">
-        <v>11.81999969482422</v>
+        <v>11.9399995803833</v>
       </c>
       <c r="E1154" t="n">
-        <v>12.06999969482422</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="F1154" t="n">
-        <v>3072424</v>
+        <v>3000855</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" s="1" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B1155" t="n">
-        <v>12.25</v>
+        <v>11.81999969482422</v>
       </c>
       <c r="C1155" t="n">
-        <v>12.46000003814697</v>
+        <v>12.09000015258789</v>
       </c>
       <c r="D1155" t="n">
-        <v>11.97000026702881</v>
+        <v>11.81999969482422</v>
       </c>
       <c r="E1155" t="n">
-        <v>11.97000026702881</v>
+        <v>12.06999969482422</v>
       </c>
       <c r="F1155" t="n">
-        <v>9880608</v>
+        <v>3072424</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B1156" t="n">
-        <v>12.47000026702881</v>
+        <v>12.25</v>
       </c>
       <c r="C1156" t="n">
-        <v>12.60999965667725</v>
+        <v>12.46000003814697</v>
       </c>
       <c r="D1156" t="n">
-        <v>12.28999996185303</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="E1156" t="n">
-        <v>12.36999988555908</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="F1156" t="n">
-        <v>4920058</v>
+        <v>9880608</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" s="1" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B1157" t="n">
-        <v>11.97999954223633</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="C1157" t="n">
-        <v>12.47000026702881</v>
+        <v>12.60999965667725</v>
       </c>
       <c r="D1157" t="n">
-        <v>11.9399995803833</v>
+        <v>12.28999996185303</v>
       </c>
       <c r="E1157" t="n">
-        <v>12.47000026702881</v>
+        <v>12.36999988555908</v>
       </c>
       <c r="F1157" t="n">
-        <v>5014997</v>
+        <v>4920058</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B1158" t="n">
-        <v>12.22999954223633</v>
+        <v>11.97999954223633</v>
       </c>
       <c r="C1158" t="n">
-        <v>12.22999954223633</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="D1158" t="n">
-        <v>11.85999965667725</v>
+        <v>11.9399995803833</v>
       </c>
       <c r="E1158" t="n">
-        <v>12.10000038146973</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="F1158" t="n">
-        <v>3580487</v>
+        <v>5014997</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" s="1" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B1159" t="n">
-        <v>12.17000007629395</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="C1159" t="n">
-        <v>12.27000045776367</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="D1159" t="n">
-        <v>12.05000019073486</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="E1159" t="n">
-        <v>12.0600004196167</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="F1159" t="n">
-        <v>4549045</v>
+        <v>3580487</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B1160" t="n">
-        <v>12.18000030517578</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="C1160" t="n">
-        <v>12.47000026702881</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="D1160" t="n">
-        <v>12.17000007629395</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="E1160" t="n">
-        <v>12.23999977111816</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="F1160" t="n">
-        <v>4709084</v>
+        <v>4549045</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B1161" t="n">
-        <v>12.3100004196167</v>
+        <v>12.18000030517578</v>
       </c>
       <c r="C1161" t="n">
-        <v>12.4399995803833</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="D1161" t="n">
-        <v>12.19999980926514</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="E1161" t="n">
-        <v>12.30000019073486</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="F1161" t="n">
-        <v>3875531</v>
+        <v>4709084</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B1162" t="n">
-        <v>11.97000026702881</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="C1162" t="n">
+        <v>12.4399995803833</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>12.19999980926514</v>
+      </c>
+      <c r="E1162" t="n">
         <v>12.30000019073486</v>
       </c>
-      <c r="D1162" t="n">
-        <v>11.88000011444092</v>
-      </c>
-      <c r="E1162" t="n">
-        <v>12.27000045776367</v>
-      </c>
       <c r="F1162" t="n">
-        <v>14181318</v>
+        <v>3875531</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B1163" t="n">
-        <v>11.60000038146973</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="C1163" t="n">
-        <v>12.13000011444092</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="D1163" t="n">
-        <v>11.60000038146973</v>
+        <v>11.88000011444092</v>
       </c>
       <c r="E1163" t="n">
-        <v>12.02999973297119</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="F1163" t="n">
-        <v>10094068</v>
+        <v>14181318</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" s="1" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B1164" t="n">
-        <v>11.72999954223633</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="C1164" t="n">
-        <v>11.85999965667725</v>
+        <v>12.13000011444092</v>
       </c>
       <c r="D1164" t="n">
-        <v>11.59000015258789</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="E1164" t="n">
-        <v>11.65999984741211</v>
+        <v>12.02999973297119</v>
       </c>
       <c r="F1164" t="n">
-        <v>3210994</v>
+        <v>10094068</v>
       </c>
     </row>
     <row r="1165">
@@ -23772,19 +23772,39 @@
         <v>46248</v>
       </c>
       <c r="B1168" t="n">
-        <v>13.16</v>
+        <v>13.15999984741211</v>
       </c>
       <c r="C1168" t="n">
-        <v>13.88</v>
+        <v>13.88000011444092</v>
       </c>
       <c r="D1168" t="n">
-        <v>13.03</v>
+        <v>13.02999973297119</v>
       </c>
       <c r="E1168" t="n">
-        <v>13.74</v>
+        <v>13.73999977111816</v>
       </c>
       <c r="F1168" t="n">
-        <v>35211169</v>
+        <v>35211218</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B1169" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="C1169" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="D1169" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="E1169" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="F1169" t="n">
+        <v>7699163</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1169"/>
+  <dimension ref="A1:F1170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23792,19 +23792,39 @@
         <v>46251</v>
       </c>
       <c r="B1169" t="n">
-        <v>12.66</v>
+        <v>12.65999984741211</v>
       </c>
       <c r="C1169" t="n">
-        <v>13.31</v>
+        <v>13.3100004196167</v>
       </c>
       <c r="D1169" t="n">
-        <v>12.66</v>
+        <v>12.65999984741211</v>
       </c>
       <c r="E1169" t="n">
-        <v>13.15</v>
+        <v>13.14999961853027</v>
       </c>
       <c r="F1169" t="n">
         <v>7699163</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B1170" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="C1170" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="D1170" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>3527762</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1170"/>
+  <dimension ref="A1:F1171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23429,282 +23429,282 @@
     </row>
     <row r="1151">
       <c r="A1151" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B1151" t="n">
-        <v>11.81999969482422</v>
+        <v>12.07999992370605</v>
       </c>
       <c r="C1151" t="n">
-        <v>12.01000022888184</v>
+        <v>12.10999965667725</v>
       </c>
       <c r="D1151" t="n">
-        <v>11.5</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="E1151" t="n">
-        <v>11.5</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="F1151" t="n">
-        <v>6917063</v>
+        <v>6399437</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B1152" t="n">
-        <v>12.07999992370605</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="C1152" t="n">
-        <v>12.10999965667725</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="D1152" t="n">
-        <v>11.69999980926514</v>
+        <v>11.71000003814697</v>
       </c>
       <c r="E1152" t="n">
-        <v>11.85000038146973</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="F1152" t="n">
-        <v>6399437</v>
+        <v>5815264</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B1153" t="n">
-        <v>12.10000038146973</v>
+        <v>12.09000015258789</v>
       </c>
       <c r="C1153" t="n">
-        <v>12.23999977111816</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="D1153" t="n">
-        <v>11.71000003814697</v>
+        <v>11.9399995803833</v>
       </c>
       <c r="E1153" t="n">
-        <v>12.10000038146973</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="F1153" t="n">
-        <v>5815264</v>
+        <v>3000855</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B1154" t="n">
+        <v>11.81999969482422</v>
+      </c>
+      <c r="C1154" t="n">
         <v>12.09000015258789</v>
       </c>
-      <c r="C1154" t="n">
-        <v>12.27000045776367</v>
-      </c>
       <c r="D1154" t="n">
-        <v>11.9399995803833</v>
+        <v>11.81999969482422</v>
       </c>
       <c r="E1154" t="n">
-        <v>12.05000019073486</v>
+        <v>12.06999969482422</v>
       </c>
       <c r="F1154" t="n">
-        <v>3000855</v>
+        <v>3072424</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B1155" t="n">
-        <v>11.81999969482422</v>
+        <v>12.25</v>
       </c>
       <c r="C1155" t="n">
-        <v>12.09000015258789</v>
+        <v>12.46000003814697</v>
       </c>
       <c r="D1155" t="n">
-        <v>11.81999969482422</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="E1155" t="n">
-        <v>12.06999969482422</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="F1155" t="n">
-        <v>3072424</v>
+        <v>9880608</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B1156" t="n">
-        <v>12.25</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="C1156" t="n">
-        <v>12.46000003814697</v>
+        <v>12.60999965667725</v>
       </c>
       <c r="D1156" t="n">
-        <v>11.97000026702881</v>
+        <v>12.28999996185303</v>
       </c>
       <c r="E1156" t="n">
-        <v>11.97000026702881</v>
+        <v>12.36999988555908</v>
       </c>
       <c r="F1156" t="n">
-        <v>9880608</v>
+        <v>4920058</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B1157" t="n">
+        <v>11.97999954223633</v>
+      </c>
+      <c r="C1157" t="n">
         <v>12.47000026702881</v>
       </c>
-      <c r="C1157" t="n">
-        <v>12.60999965667725</v>
-      </c>
       <c r="D1157" t="n">
-        <v>12.28999996185303</v>
+        <v>11.9399995803833</v>
       </c>
       <c r="E1157" t="n">
-        <v>12.36999988555908</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="F1157" t="n">
-        <v>4920058</v>
+        <v>5014997</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B1158" t="n">
-        <v>11.97999954223633</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="C1158" t="n">
-        <v>12.47000026702881</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="D1158" t="n">
-        <v>11.9399995803833</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="E1158" t="n">
-        <v>12.47000026702881</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="F1158" t="n">
-        <v>5014997</v>
+        <v>3580487</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B1159" t="n">
-        <v>12.22999954223633</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="C1159" t="n">
-        <v>12.22999954223633</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="D1159" t="n">
-        <v>11.85999965667725</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="E1159" t="n">
-        <v>12.10000038146973</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="F1159" t="n">
-        <v>3580487</v>
+        <v>4549045</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1160" t="n">
+        <v>12.18000030517578</v>
+      </c>
+      <c r="C1160" t="n">
+        <v>12.47000026702881</v>
+      </c>
+      <c r="D1160" t="n">
         <v>12.17000007629395</v>
       </c>
-      <c r="C1160" t="n">
-        <v>12.27000045776367</v>
-      </c>
-      <c r="D1160" t="n">
-        <v>12.05000019073486</v>
-      </c>
       <c r="E1160" t="n">
-        <v>12.0600004196167</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="F1160" t="n">
-        <v>4549045</v>
+        <v>4709084</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1161" t="n">
-        <v>12.18000030517578</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="C1161" t="n">
-        <v>12.47000026702881</v>
+        <v>12.4399995803833</v>
       </c>
       <c r="D1161" t="n">
-        <v>12.17000007629395</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="E1161" t="n">
-        <v>12.23999977111816</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="F1161" t="n">
-        <v>4709084</v>
+        <v>3875531</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1162" t="n">
-        <v>12.3100004196167</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="C1162" t="n">
-        <v>12.4399995803833</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="D1162" t="n">
-        <v>12.19999980926514</v>
+        <v>11.88000011444092</v>
       </c>
       <c r="E1162" t="n">
-        <v>12.30000019073486</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="F1162" t="n">
-        <v>3875531</v>
+        <v>14181318</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1163" t="n">
-        <v>11.97000026702881</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="C1163" t="n">
-        <v>12.30000019073486</v>
+        <v>12.13000011444092</v>
       </c>
       <c r="D1163" t="n">
-        <v>11.88000011444092</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="E1163" t="n">
-        <v>12.27000045776367</v>
+        <v>12.02999973297119</v>
       </c>
       <c r="F1163" t="n">
-        <v>14181318</v>
+        <v>10094068</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B1164" t="n">
-        <v>11.60000038146973</v>
+        <v>11.72999954223633</v>
       </c>
       <c r="C1164" t="n">
-        <v>12.13000011444092</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="D1164" t="n">
-        <v>11.60000038146973</v>
+        <v>11.59000015258789</v>
       </c>
       <c r="E1164" t="n">
-        <v>12.02999973297119</v>
+        <v>11.65999984741211</v>
       </c>
       <c r="F1164" t="n">
-        <v>10094068</v>
+        <v>3210994</v>
       </c>
     </row>
     <row r="1165">
@@ -23812,19 +23812,39 @@
         <v>46252</v>
       </c>
       <c r="B1170" t="n">
-        <v>12.49</v>
+        <v>12.48999977111816</v>
       </c>
       <c r="C1170" t="n">
-        <v>12.96</v>
+        <v>12.96000003814697</v>
       </c>
       <c r="D1170" t="n">
-        <v>12.42</v>
+        <v>12.42000007629395</v>
       </c>
       <c r="E1170" t="n">
-        <v>12.73</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="F1170" t="n">
         <v>3527762</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B1171" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="C1171" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>4624456</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1171"/>
+  <dimension ref="A1:F1172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23429,282 +23429,282 @@
     </row>
     <row r="1151">
       <c r="A1151" s="1" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B1151" t="n">
-        <v>12.07999992370605</v>
+        <v>11.81999969482422</v>
       </c>
       <c r="C1151" t="n">
-        <v>12.10999965667725</v>
+        <v>12.01000022888184</v>
       </c>
       <c r="D1151" t="n">
-        <v>11.69999980926514</v>
+        <v>11.5</v>
       </c>
       <c r="E1151" t="n">
-        <v>11.85000038146973</v>
+        <v>11.5</v>
       </c>
       <c r="F1151" t="n">
-        <v>6399437</v>
+        <v>6917063</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" s="1" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B1152" t="n">
-        <v>12.10000038146973</v>
+        <v>12.07999992370605</v>
       </c>
       <c r="C1152" t="n">
-        <v>12.23999977111816</v>
+        <v>12.10999965667725</v>
       </c>
       <c r="D1152" t="n">
-        <v>11.71000003814697</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="E1152" t="n">
-        <v>12.10000038146973</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="F1152" t="n">
-        <v>5815264</v>
+        <v>6399437</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" s="1" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B1153" t="n">
-        <v>12.09000015258789</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="C1153" t="n">
-        <v>12.27000045776367</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="D1153" t="n">
-        <v>11.9399995803833</v>
+        <v>11.71000003814697</v>
       </c>
       <c r="E1153" t="n">
-        <v>12.05000019073486</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="F1153" t="n">
-        <v>3000855</v>
+        <v>5815264</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" s="1" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B1154" t="n">
-        <v>11.81999969482422</v>
+        <v>12.09000015258789</v>
       </c>
       <c r="C1154" t="n">
-        <v>12.09000015258789</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="D1154" t="n">
-        <v>11.81999969482422</v>
+        <v>11.9399995803833</v>
       </c>
       <c r="E1154" t="n">
-        <v>12.06999969482422</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="F1154" t="n">
-        <v>3072424</v>
+        <v>3000855</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" s="1" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B1155" t="n">
-        <v>12.25</v>
+        <v>11.81999969482422</v>
       </c>
       <c r="C1155" t="n">
-        <v>12.46000003814697</v>
+        <v>12.09000015258789</v>
       </c>
       <c r="D1155" t="n">
-        <v>11.97000026702881</v>
+        <v>11.81999969482422</v>
       </c>
       <c r="E1155" t="n">
-        <v>11.97000026702881</v>
+        <v>12.06999969482422</v>
       </c>
       <c r="F1155" t="n">
-        <v>9880608</v>
+        <v>3072424</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B1156" t="n">
-        <v>12.47000026702881</v>
+        <v>12.25</v>
       </c>
       <c r="C1156" t="n">
-        <v>12.60999965667725</v>
+        <v>12.46000003814697</v>
       </c>
       <c r="D1156" t="n">
-        <v>12.28999996185303</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="E1156" t="n">
-        <v>12.36999988555908</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="F1156" t="n">
-        <v>4920058</v>
+        <v>9880608</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" s="1" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B1157" t="n">
-        <v>11.97999954223633</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="C1157" t="n">
-        <v>12.47000026702881</v>
+        <v>12.60999965667725</v>
       </c>
       <c r="D1157" t="n">
-        <v>11.9399995803833</v>
+        <v>12.28999996185303</v>
       </c>
       <c r="E1157" t="n">
-        <v>12.47000026702881</v>
+        <v>12.36999988555908</v>
       </c>
       <c r="F1157" t="n">
-        <v>5014997</v>
+        <v>4920058</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B1158" t="n">
-        <v>12.22999954223633</v>
+        <v>11.97999954223633</v>
       </c>
       <c r="C1158" t="n">
-        <v>12.22999954223633</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="D1158" t="n">
-        <v>11.85999965667725</v>
+        <v>11.9399995803833</v>
       </c>
       <c r="E1158" t="n">
-        <v>12.10000038146973</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="F1158" t="n">
-        <v>3580487</v>
+        <v>5014997</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" s="1" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B1159" t="n">
-        <v>12.17000007629395</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="C1159" t="n">
-        <v>12.27000045776367</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="D1159" t="n">
-        <v>12.05000019073486</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="E1159" t="n">
-        <v>12.0600004196167</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="F1159" t="n">
-        <v>4549045</v>
+        <v>3580487</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B1160" t="n">
-        <v>12.18000030517578</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="C1160" t="n">
-        <v>12.47000026702881</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="D1160" t="n">
-        <v>12.17000007629395</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="E1160" t="n">
-        <v>12.23999977111816</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="F1160" t="n">
-        <v>4709084</v>
+        <v>4549045</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B1161" t="n">
-        <v>12.3100004196167</v>
+        <v>12.18000030517578</v>
       </c>
       <c r="C1161" t="n">
-        <v>12.4399995803833</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="D1161" t="n">
-        <v>12.19999980926514</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="E1161" t="n">
-        <v>12.30000019073486</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="F1161" t="n">
-        <v>3875531</v>
+        <v>4709084</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B1162" t="n">
-        <v>11.97000026702881</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="C1162" t="n">
+        <v>12.4399995803833</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>12.19999980926514</v>
+      </c>
+      <c r="E1162" t="n">
         <v>12.30000019073486</v>
       </c>
-      <c r="D1162" t="n">
-        <v>11.88000011444092</v>
-      </c>
-      <c r="E1162" t="n">
-        <v>12.27000045776367</v>
-      </c>
       <c r="F1162" t="n">
-        <v>14181318</v>
+        <v>3875531</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B1163" t="n">
-        <v>11.60000038146973</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="C1163" t="n">
-        <v>12.13000011444092</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="D1163" t="n">
-        <v>11.60000038146973</v>
+        <v>11.88000011444092</v>
       </c>
       <c r="E1163" t="n">
-        <v>12.02999973297119</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="F1163" t="n">
-        <v>10094068</v>
+        <v>14181318</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" s="1" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B1164" t="n">
-        <v>11.72999954223633</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="C1164" t="n">
-        <v>11.85999965667725</v>
+        <v>12.13000011444092</v>
       </c>
       <c r="D1164" t="n">
-        <v>11.59000015258789</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="E1164" t="n">
-        <v>11.65999984741211</v>
+        <v>12.02999973297119</v>
       </c>
       <c r="F1164" t="n">
-        <v>3210994</v>
+        <v>10094068</v>
       </c>
     </row>
     <row r="1165">
@@ -23832,19 +23832,39 @@
         <v>46253</v>
       </c>
       <c r="B1171" t="n">
-        <v>12.51</v>
+        <v>12.51000022888184</v>
       </c>
       <c r="C1171" t="n">
-        <v>12.84</v>
+        <v>12.84000015258789</v>
       </c>
       <c r="D1171" t="n">
-        <v>12.22</v>
+        <v>12.22000026702881</v>
       </c>
       <c r="E1171" t="n">
-        <v>12.55</v>
+        <v>12.55000019073486</v>
       </c>
       <c r="F1171" t="n">
         <v>4624456</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B1172" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="C1172" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>6609680</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1172"/>
+  <dimension ref="A1:F1174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23609,130 +23609,130 @@
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B1160" t="n">
-        <v>12.17000007629395</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="C1160" t="n">
-        <v>12.27000045776367</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="D1160" t="n">
-        <v>12.05000019073486</v>
+        <v>12.02000045776367</v>
       </c>
       <c r="E1160" t="n">
-        <v>12.0600004196167</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="F1160" t="n">
-        <v>4549045</v>
+        <v>4594763</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B1161" t="n">
-        <v>12.18000030517578</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="C1161" t="n">
-        <v>12.47000026702881</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="D1161" t="n">
-        <v>12.17000007629395</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="E1161" t="n">
-        <v>12.23999977111816</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="F1161" t="n">
-        <v>4709084</v>
+        <v>4549045</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B1162" t="n">
-        <v>12.3100004196167</v>
+        <v>12.18000030517578</v>
       </c>
       <c r="C1162" t="n">
-        <v>12.4399995803833</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="D1162" t="n">
-        <v>12.19999980926514</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="E1162" t="n">
-        <v>12.30000019073486</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="F1162" t="n">
-        <v>3875531</v>
+        <v>4709084</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B1163" t="n">
-        <v>11.97000026702881</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="C1163" t="n">
+        <v>12.4399995803833</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>12.19999980926514</v>
+      </c>
+      <c r="E1163" t="n">
         <v>12.30000019073486</v>
       </c>
-      <c r="D1163" t="n">
-        <v>11.88000011444092</v>
-      </c>
-      <c r="E1163" t="n">
-        <v>12.27000045776367</v>
-      </c>
       <c r="F1163" t="n">
-        <v>14181318</v>
+        <v>3875531</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B1164" t="n">
-        <v>11.60000038146973</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="C1164" t="n">
-        <v>12.13000011444092</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="D1164" t="n">
-        <v>11.60000038146973</v>
+        <v>11.88000011444092</v>
       </c>
       <c r="E1164" t="n">
-        <v>12.02999973297119</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="F1164" t="n">
-        <v>10094068</v>
+        <v>14181318</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" s="1" t="n">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="B1165" t="n">
-        <v>11.63000011444092</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="C1165" t="n">
-        <v>11.80000019073486</v>
+        <v>12.13000011444092</v>
       </c>
       <c r="D1165" t="n">
-        <v>11.46000003814697</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="E1165" t="n">
-        <v>11.78999996185303</v>
+        <v>12.02999973297119</v>
       </c>
       <c r="F1165" t="n">
-        <v>9590947</v>
+        <v>10094068</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B1166" t="n">
-        <v>11.60999965667725</v>
+        <v>11.63000011444092</v>
       </c>
       <c r="C1166" t="n">
         <v>11.80000019073486</v>
@@ -23741,130 +23741,170 @@
         <v>11.46000003814697</v>
       </c>
       <c r="E1166" t="n">
-        <v>11.65999984741211</v>
+        <v>11.78999996185303</v>
       </c>
       <c r="F1166" t="n">
-        <v>13093870</v>
+        <v>9590947</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B1167" t="n">
-        <v>12.03999996185303</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="C1167" t="n">
-        <v>12.03999996185303</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="D1167" t="n">
-        <v>11.56999969482422</v>
+        <v>11.46000003814697</v>
       </c>
       <c r="E1167" t="n">
-        <v>11.60999965667725</v>
+        <v>11.65999984741211</v>
       </c>
       <c r="F1167" t="n">
-        <v>6381643</v>
+        <v>13093870</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B1168" t="n">
-        <v>13.15999984741211</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="C1168" t="n">
-        <v>13.88000011444092</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="D1168" t="n">
-        <v>13.02999973297119</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="E1168" t="n">
-        <v>13.73999977111816</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="F1168" t="n">
-        <v>35211218</v>
+        <v>6381643</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" s="1" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B1169" t="n">
-        <v>12.65999984741211</v>
+        <v>13.15999984741211</v>
       </c>
       <c r="C1169" t="n">
-        <v>13.3100004196167</v>
+        <v>13.88000011444092</v>
       </c>
       <c r="D1169" t="n">
-        <v>12.65999984741211</v>
+        <v>13.02999973297119</v>
       </c>
       <c r="E1169" t="n">
-        <v>13.14999961853027</v>
+        <v>13.73999977111816</v>
       </c>
       <c r="F1169" t="n">
-        <v>7699163</v>
+        <v>35211218</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" s="1" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B1170" t="n">
-        <v>12.48999977111816</v>
+        <v>12.65999984741211</v>
       </c>
       <c r="C1170" t="n">
-        <v>12.96000003814697</v>
+        <v>13.3100004196167</v>
       </c>
       <c r="D1170" t="n">
-        <v>12.42000007629395</v>
+        <v>12.65999984741211</v>
       </c>
       <c r="E1170" t="n">
-        <v>12.72999954223633</v>
+        <v>13.14999961853027</v>
       </c>
       <c r="F1170" t="n">
-        <v>3527762</v>
+        <v>7699163</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" s="1" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B1171" t="n">
-        <v>12.51000022888184</v>
+        <v>12.48999977111816</v>
       </c>
       <c r="C1171" t="n">
-        <v>12.84000015258789</v>
+        <v>12.96000003814697</v>
       </c>
       <c r="D1171" t="n">
-        <v>12.22000026702881</v>
+        <v>12.42000007629395</v>
       </c>
       <c r="E1171" t="n">
-        <v>12.55000019073486</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="F1171" t="n">
-        <v>4624456</v>
+        <v>3527762</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B1172" t="n">
+        <v>12.51000022888184</v>
+      </c>
+      <c r="C1172" t="n">
+        <v>12.84000015258789</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>12.22000026702881</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>12.55000019073486</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>4624456</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="1" t="n">
         <v>46254</v>
       </c>
-      <c r="B1172" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="C1172" t="n">
-        <v>12.72</v>
-      </c>
-      <c r="D1172" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="E1172" t="n">
+      <c r="B1173" t="n">
+        <v>12.22000026702881</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>12.72000026702881</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>12.14999961853027</v>
+      </c>
+      <c r="E1173" t="n">
         <v>12.5</v>
       </c>
-      <c r="F1172" t="n">
+      <c r="F1173" t="n">
         <v>6609680</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B1174" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="C1174" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>8417623</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1174"/>
+  <dimension ref="A1:F1176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23729,30 +23729,30 @@
     </row>
     <row r="1166">
       <c r="A1166" s="1" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B1166" t="n">
-        <v>11.63000011444092</v>
+        <v>11.72999954223633</v>
       </c>
       <c r="C1166" t="n">
-        <v>11.80000019073486</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="D1166" t="n">
-        <v>11.46000003814697</v>
+        <v>11.59000015258789</v>
       </c>
       <c r="E1166" t="n">
-        <v>11.78999996185303</v>
+        <v>11.65999984741211</v>
       </c>
       <c r="F1166" t="n">
-        <v>9590947</v>
+        <v>3210994</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B1167" t="n">
-        <v>11.60999965667725</v>
+        <v>11.63000011444092</v>
       </c>
       <c r="C1167" t="n">
         <v>11.80000019073486</v>
@@ -23761,150 +23761,190 @@
         <v>11.46000003814697</v>
       </c>
       <c r="E1167" t="n">
-        <v>11.65999984741211</v>
+        <v>11.78999996185303</v>
       </c>
       <c r="F1167" t="n">
-        <v>13093870</v>
+        <v>9590947</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B1168" t="n">
-        <v>12.03999996185303</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="C1168" t="n">
-        <v>12.03999996185303</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="D1168" t="n">
-        <v>11.56999969482422</v>
+        <v>11.46000003814697</v>
       </c>
       <c r="E1168" t="n">
-        <v>11.60999965667725</v>
+        <v>11.65999984741211</v>
       </c>
       <c r="F1168" t="n">
-        <v>6381643</v>
+        <v>13093870</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B1169" t="n">
-        <v>13.15999984741211</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="C1169" t="n">
-        <v>13.88000011444092</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="D1169" t="n">
-        <v>13.02999973297119</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="E1169" t="n">
-        <v>13.73999977111816</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="F1169" t="n">
-        <v>35211218</v>
+        <v>6381643</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" s="1" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B1170" t="n">
-        <v>12.65999984741211</v>
+        <v>13.15999984741211</v>
       </c>
       <c r="C1170" t="n">
-        <v>13.3100004196167</v>
+        <v>13.88000011444092</v>
       </c>
       <c r="D1170" t="n">
-        <v>12.65999984741211</v>
+        <v>13.02999973297119</v>
       </c>
       <c r="E1170" t="n">
-        <v>13.14999961853027</v>
+        <v>13.73999977111816</v>
       </c>
       <c r="F1170" t="n">
-        <v>7699163</v>
+        <v>35211218</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" s="1" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B1171" t="n">
-        <v>12.48999977111816</v>
+        <v>12.65999984741211</v>
       </c>
       <c r="C1171" t="n">
-        <v>12.96000003814697</v>
+        <v>13.3100004196167</v>
       </c>
       <c r="D1171" t="n">
-        <v>12.42000007629395</v>
+        <v>12.65999984741211</v>
       </c>
       <c r="E1171" t="n">
-        <v>12.72999954223633</v>
+        <v>13.14999961853027</v>
       </c>
       <c r="F1171" t="n">
-        <v>3527762</v>
+        <v>7699163</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" s="1" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B1172" t="n">
-        <v>12.51000022888184</v>
+        <v>12.48999977111816</v>
       </c>
       <c r="C1172" t="n">
-        <v>12.84000015258789</v>
+        <v>12.96000003814697</v>
       </c>
       <c r="D1172" t="n">
-        <v>12.22000026702881</v>
+        <v>12.42000007629395</v>
       </c>
       <c r="E1172" t="n">
-        <v>12.55000019073486</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="F1172" t="n">
-        <v>4624456</v>
+        <v>3527762</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" s="1" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B1173" t="n">
+        <v>12.51000022888184</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>12.84000015258789</v>
+      </c>
+      <c r="D1173" t="n">
         <v>12.22000026702881</v>
       </c>
-      <c r="C1173" t="n">
-        <v>12.72000026702881</v>
-      </c>
-      <c r="D1173" t="n">
-        <v>12.14999961853027</v>
-      </c>
       <c r="E1173" t="n">
-        <v>12.5</v>
+        <v>12.55000019073486</v>
       </c>
       <c r="F1173" t="n">
-        <v>6609680</v>
+        <v>4624456</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B1174" t="n">
+        <v>12.22000026702881</v>
+      </c>
+      <c r="C1174" t="n">
+        <v>12.72000026702881</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>12.14999961853027</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>6609680</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="1" t="n">
         <v>46255</v>
       </c>
-      <c r="B1174" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="C1174" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="D1174" t="n">
+      <c r="B1175" t="n">
+        <v>12.39999961853027</v>
+      </c>
+      <c r="C1175" t="n">
+        <v>12.64000034332275</v>
+      </c>
+      <c r="D1175" t="n">
         <v>12.25</v>
       </c>
-      <c r="E1174" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F1174" t="n">
+      <c r="E1175" t="n">
+        <v>12.30000019073486</v>
+      </c>
+      <c r="F1175" t="n">
         <v>8417623</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1176" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="C1176" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>7443329</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1176"/>
+  <dimension ref="A1:F1177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23932,19 +23932,39 @@
         <v>46258</v>
       </c>
       <c r="B1176" t="n">
-        <v>12.57</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="C1176" t="n">
-        <v>12.85</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="D1176" t="n">
-        <v>12.27</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="E1176" t="n">
-        <v>12.53</v>
+        <v>12.52999973297119</v>
       </c>
       <c r="F1176" t="n">
         <v>7443329</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B1177" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="C1177" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>7291931</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1177"/>
+  <dimension ref="A1:F1178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23952,19 +23952,39 @@
         <v>46259</v>
       </c>
       <c r="B1177" t="n">
-        <v>12.85</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="C1177" t="n">
-        <v>12.86</v>
+        <v>12.85999965667725</v>
       </c>
       <c r="D1177" t="n">
-        <v>12.35</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="E1177" t="n">
-        <v>12.61</v>
+        <v>12.60999965667725</v>
       </c>
       <c r="F1177" t="n">
         <v>7291931</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B1178" t="n">
+        <v>13.01000022888184</v>
+      </c>
+      <c r="C1178" t="n">
+        <v>13.15999984741211</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>12.85000038146973</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>12.86999988555908</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>8339023</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -23729,30 +23729,30 @@
     </row>
     <row r="1166">
       <c r="A1166" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B1166" t="n">
-        <v>11.72999954223633</v>
+        <v>11.63000011444092</v>
       </c>
       <c r="C1166" t="n">
-        <v>11.85999965667725</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="D1166" t="n">
-        <v>11.59000015258789</v>
+        <v>11.46000003814697</v>
       </c>
       <c r="E1166" t="n">
-        <v>11.65999984741211</v>
+        <v>11.78999996185303</v>
       </c>
       <c r="F1166" t="n">
-        <v>3210994</v>
+        <v>9590947</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B1167" t="n">
-        <v>11.63000011444092</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="C1167" t="n">
         <v>11.80000019073486</v>
@@ -23761,230 +23761,230 @@
         <v>11.46000003814697</v>
       </c>
       <c r="E1167" t="n">
-        <v>11.78999996185303</v>
+        <v>11.65999984741211</v>
       </c>
       <c r="F1167" t="n">
-        <v>9590947</v>
+        <v>13093870</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B1168" t="n">
+        <v>12.03999996185303</v>
+      </c>
+      <c r="C1168" t="n">
+        <v>12.03999996185303</v>
+      </c>
+      <c r="D1168" t="n">
+        <v>11.56999969482422</v>
+      </c>
+      <c r="E1168" t="n">
         <v>11.60999965667725</v>
       </c>
-      <c r="C1168" t="n">
-        <v>11.80000019073486</v>
-      </c>
-      <c r="D1168" t="n">
-        <v>11.46000003814697</v>
-      </c>
-      <c r="E1168" t="n">
-        <v>11.65999984741211</v>
-      </c>
       <c r="F1168" t="n">
-        <v>13093870</v>
+        <v>6381643</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B1169" t="n">
-        <v>12.03999996185303</v>
+        <v>13.15999984741211</v>
       </c>
       <c r="C1169" t="n">
-        <v>12.03999996185303</v>
+        <v>13.88000011444092</v>
       </c>
       <c r="D1169" t="n">
-        <v>11.56999969482422</v>
+        <v>13.02999973297119</v>
       </c>
       <c r="E1169" t="n">
-        <v>11.60999965667725</v>
+        <v>13.73999977111816</v>
       </c>
       <c r="F1169" t="n">
-        <v>6381643</v>
+        <v>35211218</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B1170" t="n">
-        <v>13.15999984741211</v>
+        <v>12.65999984741211</v>
       </c>
       <c r="C1170" t="n">
-        <v>13.88000011444092</v>
+        <v>13.3100004196167</v>
       </c>
       <c r="D1170" t="n">
-        <v>13.02999973297119</v>
+        <v>12.65999984741211</v>
       </c>
       <c r="E1170" t="n">
-        <v>13.73999977111816</v>
+        <v>13.14999961853027</v>
       </c>
       <c r="F1170" t="n">
-        <v>35211218</v>
+        <v>7699163</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B1171" t="n">
-        <v>12.65999984741211</v>
+        <v>12.48999977111816</v>
       </c>
       <c r="C1171" t="n">
-        <v>13.3100004196167</v>
+        <v>12.96000003814697</v>
       </c>
       <c r="D1171" t="n">
-        <v>12.65999984741211</v>
+        <v>12.42000007629395</v>
       </c>
       <c r="E1171" t="n">
-        <v>13.14999961853027</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="F1171" t="n">
-        <v>7699163</v>
+        <v>3527762</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B1172" t="n">
-        <v>12.48999977111816</v>
+        <v>12.51000022888184</v>
       </c>
       <c r="C1172" t="n">
-        <v>12.96000003814697</v>
+        <v>12.84000015258789</v>
       </c>
       <c r="D1172" t="n">
-        <v>12.42000007629395</v>
+        <v>12.22000026702881</v>
       </c>
       <c r="E1172" t="n">
-        <v>12.72999954223633</v>
+        <v>12.55000019073486</v>
       </c>
       <c r="F1172" t="n">
-        <v>3527762</v>
+        <v>4624456</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B1173" t="n">
-        <v>12.51000022888184</v>
+        <v>12.22000026702881</v>
       </c>
       <c r="C1173" t="n">
-        <v>12.84000015258789</v>
+        <v>12.72000026702881</v>
       </c>
       <c r="D1173" t="n">
-        <v>12.22000026702881</v>
+        <v>12.14999961853027</v>
       </c>
       <c r="E1173" t="n">
-        <v>12.55000019073486</v>
+        <v>12.5</v>
       </c>
       <c r="F1173" t="n">
-        <v>4624456</v>
+        <v>6609680</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B1174" t="n">
-        <v>12.22000026702881</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="C1174" t="n">
-        <v>12.72000026702881</v>
+        <v>12.64000034332275</v>
       </c>
       <c r="D1174" t="n">
-        <v>12.14999961853027</v>
+        <v>12.25</v>
       </c>
       <c r="E1174" t="n">
-        <v>12.5</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="F1174" t="n">
-        <v>6609680</v>
+        <v>8417623</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B1175" t="n">
-        <v>12.39999961853027</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="C1175" t="n">
-        <v>12.64000034332275</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="D1175" t="n">
-        <v>12.25</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="E1175" t="n">
-        <v>12.30000019073486</v>
+        <v>12.52999973297119</v>
       </c>
       <c r="F1175" t="n">
-        <v>8417623</v>
+        <v>7443329</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B1176" t="n">
-        <v>12.56999969482422</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="C1176" t="n">
-        <v>12.85000038146973</v>
+        <v>12.85999965667725</v>
       </c>
       <c r="D1176" t="n">
-        <v>12.27000045776367</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="E1176" t="n">
-        <v>12.52999973297119</v>
+        <v>12.60999965667725</v>
       </c>
       <c r="F1176" t="n">
-        <v>7443329</v>
+        <v>7291931</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B1177" t="n">
+        <v>13.01000022888184</v>
+      </c>
+      <c r="C1177" t="n">
+        <v>13.15999984741211</v>
+      </c>
+      <c r="D1177" t="n">
         <v>12.85000038146973</v>
       </c>
-      <c r="C1177" t="n">
-        <v>12.85999965667725</v>
-      </c>
-      <c r="D1177" t="n">
-        <v>12.35000038146973</v>
-      </c>
       <c r="E1177" t="n">
-        <v>12.60999965667725</v>
+        <v>12.86999988555908</v>
       </c>
       <c r="F1177" t="n">
-        <v>7291931</v>
+        <v>8362118</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B1178" t="n">
-        <v>13.01000022888184</v>
+        <v>12.65</v>
       </c>
       <c r="C1178" t="n">
-        <v>13.15999984741211</v>
+        <v>13.04</v>
       </c>
       <c r="D1178" t="n">
-        <v>12.85000038146973</v>
+        <v>12.61</v>
       </c>
       <c r="E1178" t="n">
-        <v>12.86999988555908</v>
+        <v>12.97</v>
       </c>
       <c r="F1178" t="n">
-        <v>8339023</v>
+        <v>7171471</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1178"/>
+  <dimension ref="A1:F1180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23729,30 +23729,30 @@
     </row>
     <row r="1166">
       <c r="A1166" s="1" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B1166" t="n">
-        <v>11.63000011444092</v>
+        <v>11.72999954223633</v>
       </c>
       <c r="C1166" t="n">
-        <v>11.80000019073486</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="D1166" t="n">
-        <v>11.46000003814697</v>
+        <v>11.59000015258789</v>
       </c>
       <c r="E1166" t="n">
-        <v>11.78999996185303</v>
+        <v>11.65999984741211</v>
       </c>
       <c r="F1166" t="n">
-        <v>9590947</v>
+        <v>3210994</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B1167" t="n">
-        <v>11.60999965667725</v>
+        <v>11.63000011444092</v>
       </c>
       <c r="C1167" t="n">
         <v>11.80000019073486</v>
@@ -23761,230 +23761,270 @@
         <v>11.46000003814697</v>
       </c>
       <c r="E1167" t="n">
-        <v>11.65999984741211</v>
+        <v>11.78999996185303</v>
       </c>
       <c r="F1167" t="n">
-        <v>13093870</v>
+        <v>9590947</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B1168" t="n">
-        <v>12.03999996185303</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="C1168" t="n">
-        <v>12.03999996185303</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="D1168" t="n">
-        <v>11.56999969482422</v>
+        <v>11.46000003814697</v>
       </c>
       <c r="E1168" t="n">
-        <v>11.60999965667725</v>
+        <v>11.65999984741211</v>
       </c>
       <c r="F1168" t="n">
-        <v>6381643</v>
+        <v>13093870</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B1169" t="n">
-        <v>13.15999984741211</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="C1169" t="n">
-        <v>13.88000011444092</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="D1169" t="n">
-        <v>13.02999973297119</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="E1169" t="n">
-        <v>13.73999977111816</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="F1169" t="n">
-        <v>35211218</v>
+        <v>6381643</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" s="1" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B1170" t="n">
-        <v>12.65999984741211</v>
+        <v>13.15999984741211</v>
       </c>
       <c r="C1170" t="n">
-        <v>13.3100004196167</v>
+        <v>13.88000011444092</v>
       </c>
       <c r="D1170" t="n">
-        <v>12.65999984741211</v>
+        <v>13.02999973297119</v>
       </c>
       <c r="E1170" t="n">
-        <v>13.14999961853027</v>
+        <v>13.73999977111816</v>
       </c>
       <c r="F1170" t="n">
-        <v>7699163</v>
+        <v>35211218</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" s="1" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B1171" t="n">
-        <v>12.48999977111816</v>
+        <v>12.65999984741211</v>
       </c>
       <c r="C1171" t="n">
-        <v>12.96000003814697</v>
+        <v>13.3100004196167</v>
       </c>
       <c r="D1171" t="n">
-        <v>12.42000007629395</v>
+        <v>12.65999984741211</v>
       </c>
       <c r="E1171" t="n">
-        <v>12.72999954223633</v>
+        <v>13.14999961853027</v>
       </c>
       <c r="F1171" t="n">
-        <v>3527762</v>
+        <v>7699163</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" s="1" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B1172" t="n">
-        <v>12.51000022888184</v>
+        <v>12.48999977111816</v>
       </c>
       <c r="C1172" t="n">
-        <v>12.84000015258789</v>
+        <v>12.96000003814697</v>
       </c>
       <c r="D1172" t="n">
-        <v>12.22000026702881</v>
+        <v>12.42000007629395</v>
       </c>
       <c r="E1172" t="n">
-        <v>12.55000019073486</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="F1172" t="n">
-        <v>4624456</v>
+        <v>3527762</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" s="1" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B1173" t="n">
+        <v>12.51000022888184</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>12.84000015258789</v>
+      </c>
+      <c r="D1173" t="n">
         <v>12.22000026702881</v>
       </c>
-      <c r="C1173" t="n">
-        <v>12.72000026702881</v>
-      </c>
-      <c r="D1173" t="n">
-        <v>12.14999961853027</v>
-      </c>
       <c r="E1173" t="n">
-        <v>12.5</v>
+        <v>12.55000019073486</v>
       </c>
       <c r="F1173" t="n">
-        <v>6609680</v>
+        <v>4624456</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" s="1" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B1174" t="n">
-        <v>12.39999961853027</v>
+        <v>12.22000026702881</v>
       </c>
       <c r="C1174" t="n">
-        <v>12.64000034332275</v>
+        <v>12.72000026702881</v>
       </c>
       <c r="D1174" t="n">
-        <v>12.25</v>
+        <v>12.14999961853027</v>
       </c>
       <c r="E1174" t="n">
-        <v>12.30000019073486</v>
+        <v>12.5</v>
       </c>
       <c r="F1174" t="n">
-        <v>8417623</v>
+        <v>6609680</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" s="1" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B1175" t="n">
-        <v>12.56999969482422</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="C1175" t="n">
-        <v>12.85000038146973</v>
+        <v>12.64000034332275</v>
       </c>
       <c r="D1175" t="n">
-        <v>12.27000045776367</v>
+        <v>12.25</v>
       </c>
       <c r="E1175" t="n">
-        <v>12.52999973297119</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="F1175" t="n">
-        <v>7443329</v>
+        <v>8417623</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" s="1" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B1176" t="n">
+        <v>12.56999969482422</v>
+      </c>
+      <c r="C1176" t="n">
         <v>12.85000038146973</v>
       </c>
-      <c r="C1176" t="n">
-        <v>12.85999965667725</v>
-      </c>
       <c r="D1176" t="n">
-        <v>12.35000038146973</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="E1176" t="n">
-        <v>12.60999965667725</v>
+        <v>12.52999973297119</v>
       </c>
       <c r="F1176" t="n">
-        <v>7291931</v>
+        <v>7443329</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" s="1" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B1177" t="n">
-        <v>13.01000022888184</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="C1177" t="n">
-        <v>13.15999984741211</v>
+        <v>12.85999965667725</v>
       </c>
       <c r="D1177" t="n">
-        <v>12.85000038146973</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="E1177" t="n">
-        <v>12.86999988555908</v>
+        <v>12.60999965667725</v>
       </c>
       <c r="F1177" t="n">
-        <v>8362118</v>
+        <v>7291931</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B1178" t="n">
+        <v>13.01000022888184</v>
+      </c>
+      <c r="C1178" t="n">
+        <v>13.15999984741211</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>12.85000038146973</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>12.86999988555908</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>8362118</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="1" t="n">
         <v>46261</v>
       </c>
-      <c r="B1178" t="n">
-        <v>12.65</v>
-      </c>
-      <c r="C1178" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="D1178" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="E1178" t="n">
-        <v>12.97</v>
-      </c>
-      <c r="F1178" t="n">
+      <c r="B1179" t="n">
+        <v>12.64999961853027</v>
+      </c>
+      <c r="C1179" t="n">
+        <v>13.03999996185303</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>12.60999965667725</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>12.97000026702881</v>
+      </c>
+      <c r="F1179" t="n">
         <v>7171471</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1180" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="C1180" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>5152366</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -24012,7 +24012,7 @@
         <v>46262</v>
       </c>
       <c r="B1180" t="n">
-        <v>12.32</v>
+        <v>12.33</v>
       </c>
       <c r="C1180" t="n">
         <v>12.8</v>
@@ -24024,7 +24024,7 @@
         <v>12.69</v>
       </c>
       <c r="F1180" t="n">
-        <v>5152366</v>
+        <v>6440450</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -24011,18 +24011,10 @@
       <c r="A1180" s="1" t="n">
         <v>46262</v>
       </c>
-      <c r="B1180" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="C1180" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="D1180" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="E1180" t="n">
-        <v>12.69</v>
-      </c>
+      <c r="B1180" t="inlineStr"/>
+      <c r="C1180" t="inlineStr"/>
+      <c r="D1180" t="inlineStr"/>
+      <c r="E1180" t="inlineStr"/>
       <c r="F1180" t="n">
         <v>6440450</v>
       </c>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1180"/>
+  <dimension ref="A1:F1182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24011,12 +24011,60 @@
       <c r="A1180" s="1" t="n">
         <v>46262</v>
       </c>
-      <c r="B1180" t="inlineStr"/>
-      <c r="C1180" t="inlineStr"/>
-      <c r="D1180" t="inlineStr"/>
-      <c r="E1180" t="inlineStr"/>
+      <c r="B1180" t="n">
+        <v>12.32999992370605</v>
+      </c>
+      <c r="C1180" t="n">
+        <v>12.80000019073486</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>12.27000045776367</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>12.6899995803833</v>
+      </c>
       <c r="F1180" t="n">
-        <v>6440450</v>
+        <v>6442077</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1181" t="n">
+        <v>12.47999954223633</v>
+      </c>
+      <c r="C1181" t="n">
+        <v>12.53999996185303</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>12.1899995803833</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>12.32999992370605</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>5752024</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B1182" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="C1182" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>13759651</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1182"/>
+  <dimension ref="A1:F1183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24052,19 +24052,39 @@
         <v>46266</v>
       </c>
       <c r="B1182" t="n">
-        <v>12.34</v>
+        <v>12.34000015258789</v>
       </c>
       <c r="C1182" t="n">
-        <v>12.72</v>
+        <v>12.72000026702881</v>
       </c>
       <c r="D1182" t="n">
-        <v>12.3</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="E1182" t="n">
-        <v>12.42</v>
+        <v>12.42000007629395</v>
       </c>
       <c r="F1182" t="n">
         <v>13759651</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1183" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1183" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>11115889</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1183"/>
+  <dimension ref="A1:F1184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24075,16 +24075,36 @@
         <v>13</v>
       </c>
       <c r="C1183" t="n">
-        <v>13.09</v>
+        <v>13.09000015258789</v>
       </c>
       <c r="D1183" t="n">
-        <v>12.34</v>
+        <v>12.34000015258789</v>
       </c>
       <c r="E1183" t="n">
-        <v>12.35</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="F1183" t="n">
         <v>11115889</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1184" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="C1184" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>8212489</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1184"/>
+  <dimension ref="A1:F1185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24092,19 +24092,39 @@
         <v>46268</v>
       </c>
       <c r="B1184" t="n">
-        <v>13.11</v>
+        <v>13.10999965667725</v>
       </c>
       <c r="C1184" t="n">
-        <v>13.4</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="D1184" t="n">
-        <v>12.99</v>
+        <v>12.98999977111816</v>
       </c>
       <c r="E1184" t="n">
-        <v>13.1</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="F1184" t="n">
         <v>8212489</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1185" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="C1185" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>5251159</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -24112,16 +24112,16 @@
         <v>46269</v>
       </c>
       <c r="B1185" t="n">
-        <v>13.22</v>
+        <v>13.22000026702881</v>
       </c>
       <c r="C1185" t="n">
-        <v>13.24</v>
+        <v>13.23999977111816</v>
       </c>
       <c r="D1185" t="n">
-        <v>12.94</v>
+        <v>12.9399995803833</v>
       </c>
       <c r="E1185" t="n">
-        <v>13.11</v>
+        <v>13.10999965667725</v>
       </c>
       <c r="F1185" t="n">
         <v>5251159</v>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1185"/>
+  <dimension ref="A1:F1186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24127,6 +24127,26 @@
         <v>5251159</v>
       </c>
     </row>
+    <row r="1186">
+      <c r="A1186" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1186" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="C1186" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>11468000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1186"/>
+  <dimension ref="A1:F1187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24132,19 +24132,39 @@
         <v>46273</v>
       </c>
       <c r="B1186" t="n">
-        <v>12.92</v>
+        <v>12.92000007629395</v>
       </c>
       <c r="C1186" t="n">
-        <v>13.34</v>
+        <v>13.34000015258789</v>
       </c>
       <c r="D1186" t="n">
-        <v>12.91</v>
+        <v>12.90999984741211</v>
       </c>
       <c r="E1186" t="n">
         <v>13.25</v>
       </c>
       <c r="F1186" t="n">
         <v>11468000</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1187" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="C1187" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>7400862</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1187"/>
+  <dimension ref="A1:F1188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24155,16 +24155,36 @@
         <v>12.75</v>
       </c>
       <c r="C1187" t="n">
-        <v>12.98</v>
+        <v>12.97999954223633</v>
       </c>
       <c r="D1187" t="n">
-        <v>12.69</v>
+        <v>12.6899995803833</v>
       </c>
       <c r="E1187" t="n">
-        <v>12.91</v>
+        <v>12.90999984741211</v>
       </c>
       <c r="F1187" t="n">
         <v>7400862</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1188" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="C1188" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>8898635</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1188"/>
+  <dimension ref="A1:F1189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24172,19 +24172,39 @@
         <v>46275</v>
       </c>
       <c r="B1188" t="n">
-        <v>12.7</v>
+        <v>12.69999980926514</v>
       </c>
       <c r="C1188" t="n">
-        <v>13.04</v>
+        <v>13.03999996185303</v>
       </c>
       <c r="D1188" t="n">
-        <v>12.58</v>
+        <v>12.57999992370605</v>
       </c>
       <c r="E1188" t="n">
-        <v>12.72</v>
+        <v>12.72000026702881</v>
       </c>
       <c r="F1188" t="n">
         <v>8898635</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1189" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="C1189" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>10821188</v>
       </c>
     </row>
   </sheetData>
